--- a/output/quickfixclose0_all_markets_daily.xlsx
+++ b/output/quickfixclose0_all_markets_daily.xlsx
@@ -549,11 +549,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -597,11 +597,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -645,11 +645,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -693,11 +693,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -741,11 +741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -789,11 +789,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -885,11 +885,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -933,11 +933,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -981,11 +981,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -1077,11 +1077,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1173,11 +1173,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1221,11 +1221,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
+          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose0_all_markets_daily.xlsx
+++ b/output/quickfixclose0_all_markets_daily.xlsx
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
+          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose0_all_markets_daily.xlsx
+++ b/output/quickfixclose0_all_markets_daily.xlsx
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose0_all_markets_daily.xlsx
+++ b/output/quickfixclose0_all_markets_daily.xlsx
@@ -549,11 +549,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -597,11 +597,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -645,11 +645,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -693,11 +693,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -741,11 +741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -789,11 +789,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -885,11 +885,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -933,11 +933,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -981,11 +981,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -1077,11 +1077,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1173,11 +1173,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1221,11 +1221,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose0_all_markets_daily.xlsx
+++ b/output/quickfixclose0_all_markets_daily.xlsx
@@ -549,11 +549,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -597,11 +597,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -645,17 +645,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -673,10 +673,10 @@
         <v>100</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12.54</v>
+        <v>12.65</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>112535.61</v>
+        <v>112645.26</v>
       </c>
     </row>
     <row r="5">
@@ -693,11 +693,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -741,11 +741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -789,11 +789,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -826,28 +826,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -865,37 +865,37 @@
         <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.42</v>
+        <v>6.57</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106418.3</v>
+        <v>106568.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -913,37 +913,37 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5.14</v>
+        <v>6.42</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>105136.62</v>
+        <v>106418.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -961,16 +961,16 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>104999.08</v>
+        <v>105136.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -981,17 +981,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1009,37 +1009,37 @@
         <v>100</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>104567.64</v>
+        <v>104999.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1057,37 +1057,37 @@
         <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>103503.61</v>
+        <v>103796.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1105,16 +1105,16 @@
         <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>103337.33</v>
+        <v>103503.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1125,17 +1125,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1153,10 +1153,10 @@
         <v>100</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2.23</v>
+        <v>3.34</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>102229.41</v>
+        <v>103337.33</v>
       </c>
     </row>
     <row r="15">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2.13</v>
+        <v>2.64</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102127.47</v>
+        <v>102635.3</v>
       </c>
     </row>
     <row r="16">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5299,11 +5299,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5312,25 +5312,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H51" t="n">
-        <v>0.006454</v>
+        <v>4363.8</v>
       </c>
       <c r="J51" t="n">
-        <v>0.006391</v>
+        <v>4299.6</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5338,16 +5338,16 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="N51" t="n">
-        <v>100000</v>
+        <v>112535.61</v>
       </c>
       <c r="O51" t="n">
-        <v>100716.22</v>
+        <v>112645.26</v>
       </c>
     </row>
     <row r="52">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5366,12 +5366,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5381,10 +5381,10 @@
         <v>0.006417</v>
       </c>
       <c r="H52" t="n">
-        <v>0.006446</v>
+        <v>0.006454</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0064</v>
+        <v>0.006391</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5392,26 +5392,26 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="N52" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O52" t="n">
         <v>100716.22</v>
-      </c>
-      <c r="O52" t="n">
-        <v>101306.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5420,25 +5420,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H53" t="n">
-        <v>239.73</v>
+        <v>0.006446</v>
       </c>
       <c r="J53" t="n">
-        <v>237.27</v>
+        <v>0.0064</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5446,16 +5446,16 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.6716</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2.6716</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>100000</v>
+        <v>100716.22</v>
       </c>
       <c r="O53" t="n">
-        <v>102671.64</v>
+        <v>101306.62</v>
       </c>
     </row>
     <row r="54">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5489,10 +5489,10 @@
         <v>239.06</v>
       </c>
       <c r="H54" t="n">
-        <v>239.76</v>
+        <v>239.73</v>
       </c>
       <c r="J54" t="n">
-        <v>236.8</v>
+        <v>237.27</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5500,16 +5500,16 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2286</v>
+        <v>2.6716</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3.2286</v>
+        <v>2.6716</v>
       </c>
       <c r="N54" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O54" t="n">
         <v>102671.64</v>
-      </c>
-      <c r="O54" t="n">
-        <v>105986.47</v>
       </c>
     </row>
     <row r="55">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5528,25 +5528,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H55" t="n">
-        <v>251.91</v>
+        <v>239.76</v>
       </c>
       <c r="J55" t="n">
-        <v>251.07</v>
+        <v>236.8</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5554,16 +5554,16 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.5455</v>
+        <v>3.2286</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1.5455</v>
+        <v>3.2286</v>
       </c>
       <c r="N55" t="n">
+        <v>102671.64</v>
+      </c>
+      <c r="O55" t="n">
         <v>105986.47</v>
-      </c>
-      <c r="O55" t="n">
-        <v>107624.44</v>
       </c>
     </row>
     <row r="56">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5582,25 +5582,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>251.45</v>
+        <v>251.58</v>
       </c>
       <c r="H56" t="n">
         <v>251.91</v>
       </c>
       <c r="J56" t="n">
-        <v>247.62</v>
+        <v>251.07</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>8.3261</v>
+        <v>1.5455</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8.3261</v>
+        <v>1.5455</v>
       </c>
       <c r="N56" t="n">
+        <v>105986.47</v>
+      </c>
+      <c r="O56" t="n">
         <v>107624.44</v>
-      </c>
-      <c r="O56" t="n">
-        <v>116585.35</v>
       </c>
     </row>
     <row r="57">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5636,25 +5636,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>255.38</v>
+        <v>251.45</v>
       </c>
       <c r="H57" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="J57" t="n">
-        <v>253</v>
+        <v>247.62</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5662,16 +5662,16 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.904</v>
+        <v>8.3261</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1.904</v>
+        <v>8.3261</v>
       </c>
       <c r="N57" t="n">
+        <v>107624.44</v>
+      </c>
+      <c r="O57" t="n">
         <v>116585.35</v>
-      </c>
-      <c r="O57" t="n">
-        <v>118805.13</v>
       </c>
     </row>
     <row r="58">
@@ -5681,34 +5681,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H58" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="J58" t="n">
-        <v>237.62</v>
+        <v>253</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5716,16 +5716,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.881</v>
+        <v>1.904</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.881</v>
+        <v>1.904</v>
       </c>
       <c r="N58" t="n">
+        <v>116585.35</v>
+      </c>
+      <c r="O58" t="n">
         <v>118805.13</v>
-      </c>
-      <c r="O58" t="n">
-        <v>122227.85</v>
       </c>
     </row>
     <row r="59">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5759,10 +5759,10 @@
         <v>235.2</v>
       </c>
       <c r="H59" t="n">
-        <v>234.39</v>
+        <v>234.36</v>
       </c>
       <c r="J59" t="n">
-        <v>235.25</v>
+        <v>237.62</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5770,26 +5770,26 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.0617</v>
+        <v>2.881</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.0617</v>
+        <v>2.881</v>
       </c>
       <c r="N59" t="n">
+        <v>118805.13</v>
+      </c>
+      <c r="O59" t="n">
         <v>122227.85</v>
-      </c>
-      <c r="O59" t="n">
-        <v>122303.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5798,25 +5798,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H60" t="n">
-        <v>5.6849</v>
+        <v>234.39</v>
       </c>
       <c r="J60" t="n">
-        <v>5.821</v>
+        <v>235.25</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5824,16 +5824,16 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.5734</v>
+        <v>0.0617</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.5734</v>
+        <v>0.0617</v>
       </c>
       <c r="N60" t="n">
-        <v>100000</v>
+        <v>122227.85</v>
       </c>
       <c r="O60" t="n">
-        <v>100573.41</v>
+        <v>122303.3</v>
       </c>
     </row>
     <row r="61">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5867,10 +5867,10 @@
         <v>5.7714</v>
       </c>
       <c r="H61" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="J61" t="n">
-        <v>5.803</v>
+        <v>5.821</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5878,16 +5878,16 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.3362</v>
+        <v>0.5734</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.3362</v>
+        <v>0.5734</v>
       </c>
       <c r="N61" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O61" t="n">
         <v>100573.41</v>
-      </c>
-      <c r="O61" t="n">
-        <v>100911.51</v>
       </c>
     </row>
     <row r="62">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5906,25 +5906,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H62" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="J62" t="n">
-        <v>5.4725</v>
+        <v>5.803</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5932,16 +5932,16 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.362</v>
+        <v>0.3362</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2.362</v>
+        <v>0.3362</v>
       </c>
       <c r="N62" t="n">
+        <v>100573.41</v>
+      </c>
+      <c r="O62" t="n">
         <v>100911.51</v>
-      </c>
-      <c r="O62" t="n">
-        <v>103295.06</v>
       </c>
     </row>
     <row r="63">
@@ -5951,34 +5951,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H63" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="J63" t="n">
-        <v>6.085</v>
+        <v>5.4725</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5986,26 +5986,26 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.2019</v>
+        <v>2.362</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.2019</v>
+        <v>2.362</v>
       </c>
       <c r="N63" t="n">
+        <v>100911.51</v>
+      </c>
+      <c r="O63" t="n">
         <v>103295.06</v>
-      </c>
-      <c r="O63" t="n">
-        <v>103503.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6014,25 +6014,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H64" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="J64" t="n">
-        <v>3.295</v>
+        <v>6.085</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.2041</v>
+        <v>0.2019</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.2041</v>
+        <v>0.2019</v>
       </c>
       <c r="N64" t="n">
-        <v>100000</v>
+        <v>103295.06</v>
       </c>
       <c r="O64" t="n">
-        <v>100204.08</v>
+        <v>103503.61</v>
       </c>
     </row>
     <row r="65">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -6083,10 +6083,10 @@
         <v>3.305</v>
       </c>
       <c r="H65" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J65" t="n">
-        <v>3.212</v>
+        <v>3.295</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6094,16 +6094,16 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.8235</v>
+        <v>0.2041</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1.8235</v>
+        <v>0.2041</v>
       </c>
       <c r="N65" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O65" t="n">
         <v>100204.08</v>
-      </c>
-      <c r="O65" t="n">
-        <v>102031.33</v>
       </c>
     </row>
     <row r="66">
@@ -6113,34 +6113,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H66" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J66" t="n">
-        <v>2.722</v>
+        <v>3.212</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6148,26 +6148,26 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.28</v>
+        <v>1.8235</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1.28</v>
+        <v>1.8235</v>
       </c>
       <c r="N66" t="n">
+        <v>100204.08</v>
+      </c>
+      <c r="O66" t="n">
         <v>102031.33</v>
-      </c>
-      <c r="O66" t="n">
-        <v>103337.33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6176,25 +6176,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H67" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J67" t="n">
-        <v>1385.9</v>
+        <v>2.722</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6202,16 +6202,16 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="N67" t="n">
-        <v>100000</v>
+        <v>102031.33</v>
       </c>
       <c r="O67" t="n">
-        <v>101500</v>
+        <v>103337.33</v>
       </c>
     </row>
     <row r="68">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6230,25 +6230,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H68" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J68" t="n">
-        <v>1193.2</v>
+        <v>1385.9</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6256,53 +6256,53 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.4474</v>
+        <v>1.5</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3.4474</v>
+        <v>1.5</v>
       </c>
       <c r="N68" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O68" t="n">
         <v>101500</v>
-      </c>
-      <c r="O68" t="n">
-        <v>104999.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H69" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J69" t="n">
-        <v>2062.3</v>
+        <v>1193.2</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6310,16 +6310,16 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.7663</v>
+        <v>3.4474</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.7663</v>
+        <v>3.4474</v>
       </c>
       <c r="N69" t="n">
-        <v>100000</v>
+        <v>101500</v>
       </c>
       <c r="O69" t="n">
-        <v>100766.32</v>
+        <v>104999.08</v>
       </c>
     </row>
     <row r="70">
@@ -6329,34 +6329,34 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H70" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J70" t="n">
-        <v>1662</v>
+        <v>2062.3</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6364,16 +6364,16 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0.7663</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1</v>
+        <v>0.7663</v>
       </c>
       <c r="N70" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O70" t="n">
         <v>100766.32</v>
-      </c>
-      <c r="O70" t="n">
-        <v>101773.99</v>
       </c>
     </row>
     <row r="71">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6392,25 +6392,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H71" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J71" t="n">
-        <v>1603</v>
+        <v>1662</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6418,16 +6418,16 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.6342</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.6342</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
+        <v>100766.32</v>
+      </c>
+      <c r="O71" t="n">
         <v>101773.99</v>
-      </c>
-      <c r="O71" t="n">
-        <v>102419.46</v>
       </c>
     </row>
     <row r="72">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6446,25 +6446,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H72" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="J72" t="n">
-        <v>1599.9</v>
+        <v>1603</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6472,53 +6472,53 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.0974</v>
+        <v>0.6342</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.0974</v>
+        <v>0.6342</v>
       </c>
       <c r="N72" t="n">
+        <v>101773.99</v>
+      </c>
+      <c r="O72" t="n">
         <v>102419.46</v>
-      </c>
-      <c r="O72" t="n">
-        <v>104567.64</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H73" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J73" t="n">
-        <v>27776</v>
+        <v>1599.9</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6526,26 +6526,26 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.2294</v>
+        <v>2.0974</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2.2294</v>
+        <v>2.0974</v>
       </c>
       <c r="N73" t="n">
-        <v>100000</v>
+        <v>102419.46</v>
       </c>
       <c r="O73" t="n">
-        <v>102229.41</v>
+        <v>104567.64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6554,25 +6554,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H74" t="n">
-        <v>7223.26</v>
+        <v>1798.4</v>
       </c>
       <c r="J74" t="n">
-        <v>7171</v>
+        <v>1746.9</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6580,26 +6580,26 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.1275</v>
+        <v>0.7882</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2.1275</v>
+        <v>0.7882</v>
       </c>
       <c r="N74" t="n">
-        <v>100000</v>
+        <v>104567.64</v>
       </c>
       <c r="O74" t="n">
-        <v>102127.47</v>
+        <v>105391.83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6608,25 +6608,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>6957.43</v>
+        <v>1769.6</v>
       </c>
       <c r="H75" t="n">
-        <v>6965.7</v>
+        <v>1798</v>
       </c>
       <c r="J75" t="n">
-        <v>6920.93</v>
+        <v>1737.9</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6634,26 +6634,26 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>4.4135</v>
+        <v>1.1162</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4.4135</v>
+        <v>1.1162</v>
       </c>
       <c r="N75" t="n">
-        <v>100000</v>
+        <v>105391.83</v>
       </c>
       <c r="O75" t="n">
-        <v>104413.54</v>
+        <v>106568.21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6662,25 +6662,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>6982.4</v>
+        <v>27907</v>
       </c>
       <c r="H76" t="n">
-        <v>6988.83</v>
+        <v>27965.76</v>
       </c>
       <c r="J76" t="n">
-        <v>6978.6</v>
+        <v>27776</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6688,26 +6688,26 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.591</v>
+        <v>2.2294</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>0.591</v>
+        <v>2.2294</v>
       </c>
       <c r="N76" t="n">
-        <v>104413.54</v>
+        <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>105030.61</v>
+        <v>102229.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6716,25 +6716,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H77" t="n">
-        <v>6992.85</v>
+        <v>30074.01</v>
       </c>
       <c r="J77" t="n">
-        <v>6969.01</v>
+        <v>29615</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6742,26 +6742,26 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.2813</v>
+        <v>1.533</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1.2813</v>
+        <v>1.533</v>
       </c>
       <c r="N77" t="n">
-        <v>105030.61</v>
+        <v>102229.41</v>
       </c>
       <c r="O77" t="n">
-        <v>106376.4</v>
+        <v>103796.61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6770,25 +6770,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H78" t="n">
-        <v>6991.93</v>
+        <v>7223.26</v>
       </c>
       <c r="J78" t="n">
-        <v>6976.44</v>
+        <v>7171</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6796,26 +6796,26 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.6254</v>
+        <v>2.1275</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.6254</v>
+        <v>2.1275</v>
       </c>
       <c r="N78" t="n">
-        <v>106376.4</v>
+        <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>107041.68</v>
+        <v>102127.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6824,25 +6824,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H79" t="n">
-        <v>6986.84</v>
+        <v>7820.26</v>
       </c>
       <c r="J79" t="n">
-        <v>6941.81</v>
+        <v>7749.5</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6850,16 +6850,16 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>9.1419</v>
+        <v>0.4972</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9.1419</v>
+        <v>0.4972</v>
       </c>
       <c r="N79" t="n">
-        <v>107041.68</v>
+        <v>102127.47</v>
       </c>
       <c r="O79" t="n">
-        <v>116827.31</v>
+        <v>102635.3</v>
       </c>
     </row>
     <row r="80">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6878,25 +6878,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H80" t="n">
-        <v>6993.49</v>
+        <v>6965.7</v>
       </c>
       <c r="J80" t="n">
-        <v>6941.47</v>
+        <v>6920.93</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6904,16 +6904,16 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.6907</v>
+        <v>4.4135</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3.6907</v>
+        <v>4.4135</v>
       </c>
       <c r="N80" t="n">
-        <v>116827.31</v>
+        <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>121139.07</v>
+        <v>104413.54</v>
       </c>
     </row>
     <row r="81">
@@ -6923,34 +6923,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H81" t="n">
-        <v>6770.77</v>
+        <v>6988.83</v>
       </c>
       <c r="J81" t="n">
-        <v>6830.71</v>
+        <v>6978.6</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6958,26 +6958,26 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.5366</v>
+        <v>0.591</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1.5366</v>
+        <v>0.591</v>
       </c>
       <c r="N81" t="n">
-        <v>121139.07</v>
+        <v>104413.54</v>
       </c>
       <c r="O81" t="n">
-        <v>123000.5</v>
+        <v>105030.61</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6986,25 +6986,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H82" t="n">
-        <v>88.001</v>
+        <v>6992.85</v>
       </c>
       <c r="J82" t="n">
-        <v>85.59099999999999</v>
+        <v>6969.01</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7012,53 +7012,53 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.2552</v>
+        <v>1.2813</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.2552</v>
+        <v>1.2813</v>
       </c>
       <c r="N82" t="n">
-        <v>100000</v>
+        <v>105030.61</v>
       </c>
       <c r="O82" t="n">
-        <v>100255.21</v>
+        <v>106376.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H83" t="n">
-        <v>71.999</v>
+        <v>6991.93</v>
       </c>
       <c r="J83" t="n">
-        <v>75.91200000000001</v>
+        <v>6976.44</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7066,26 +7066,26 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.1209</v>
+        <v>0.6254</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1.1209</v>
+        <v>0.6254</v>
       </c>
       <c r="N83" t="n">
-        <v>100255.21</v>
+        <v>106376.4</v>
       </c>
       <c r="O83" t="n">
-        <v>101378.94</v>
+        <v>107041.68</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7094,25 +7094,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H84" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="J84" t="n">
-        <v>14.99</v>
+        <v>6941.81</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7120,26 +7120,26 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.0385</v>
+        <v>9.1419</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0.0385</v>
+        <v>9.1419</v>
       </c>
       <c r="N84" t="n">
-        <v>100000</v>
+        <v>107041.68</v>
       </c>
       <c r="O84" t="n">
-        <v>100038.46</v>
+        <v>116827.31</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H85" t="n">
-        <v>15.18</v>
+        <v>6993.49</v>
       </c>
       <c r="J85" t="n">
-        <v>14.85</v>
+        <v>6941.47</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7174,53 +7174,53 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.8333</v>
+        <v>3.6907</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>0.8333</v>
+        <v>3.6907</v>
       </c>
       <c r="N85" t="n">
-        <v>100038.46</v>
+        <v>116827.31</v>
       </c>
       <c r="O85" t="n">
-        <v>100872.12</v>
+        <v>121139.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H86" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="J86" t="n">
-        <v>20.88</v>
+        <v>6830.71</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7228,22 +7228,22 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.0556</v>
+        <v>1.5366</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>0.0556</v>
+        <v>1.5366</v>
       </c>
       <c r="N86" t="n">
-        <v>100000</v>
+        <v>121139.07</v>
       </c>
       <c r="O86" t="n">
-        <v>100055.56</v>
+        <v>123000.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -7256,25 +7256,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H87" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8589</v>
+        <v>85.59099999999999</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7282,22 +7282,22 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.087</v>
+        <v>0.2552</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1.087</v>
+        <v>0.2552</v>
       </c>
       <c r="N87" t="n">
         <v>100000</v>
       </c>
       <c r="O87" t="n">
-        <v>101086.96</v>
+        <v>100255.21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -7305,30 +7305,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8649</v>
+        <v>71.999</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8612</v>
+        <v>75.91200000000001</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7336,26 +7336,26 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.0571</v>
+        <v>1.1209</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>0.0571</v>
+        <v>1.1209</v>
       </c>
       <c r="N88" t="n">
-        <v>101086.96</v>
+        <v>100255.21</v>
       </c>
       <c r="O88" t="n">
-        <v>101144.72</v>
+        <v>101378.94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7364,25 +7364,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8658</v>
+        <v>15.26</v>
       </c>
       <c r="J89" t="n">
-        <v>0.8605</v>
+        <v>14.99</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7390,53 +7390,53 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.2045</v>
+        <v>0.0385</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>0.2045</v>
+        <v>0.0385</v>
       </c>
       <c r="N89" t="n">
-        <v>101144.72</v>
+        <v>100000</v>
       </c>
       <c r="O89" t="n">
-        <v>101351.61</v>
+        <v>100038.46</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H90" t="n">
-        <v>0.8436</v>
+        <v>15.18</v>
       </c>
       <c r="J90" t="n">
-        <v>0.8498</v>
+        <v>14.85</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7444,22 +7444,22 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="N90" t="n">
-        <v>101351.61</v>
+        <v>100038.46</v>
       </c>
       <c r="O90" t="n">
-        <v>102365.12</v>
+        <v>100872.12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -7472,25 +7472,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H91" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="J91" t="n">
-        <v>116.15</v>
+        <v>20.88</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7498,26 +7498,26 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.2069</v>
+        <v>0.0556</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1.2069</v>
+        <v>0.0556</v>
       </c>
       <c r="N91" t="n">
         <v>100000</v>
       </c>
       <c r="O91" t="n">
-        <v>101206.9</v>
+        <v>100055.56</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7526,25 +7526,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H92" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="J92" t="n">
-        <v>117.9</v>
+        <v>0.8589</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7552,26 +7552,26 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.8571</v>
+        <v>1.087</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>0.8571</v>
+        <v>1.087</v>
       </c>
       <c r="N92" t="n">
-        <v>101206.9</v>
+        <v>100000</v>
       </c>
       <c r="O92" t="n">
-        <v>102074.38</v>
+        <v>101086.96</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7580,25 +7580,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>118.08</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H93" t="n">
-        <v>118.16</v>
+        <v>0.8649</v>
       </c>
       <c r="J93" t="n">
-        <v>117.84</v>
+        <v>0.8612</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7606,53 +7606,53 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3</v>
+        <v>0.0571</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3</v>
+        <v>0.0571</v>
       </c>
       <c r="N93" t="n">
-        <v>102074.38</v>
+        <v>101086.96</v>
       </c>
       <c r="O93" t="n">
-        <v>105136.62</v>
+        <v>101144.72</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="J94" t="n">
-        <v>98.005</v>
+        <v>0.8605</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7660,26 +7660,26 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.7796</v>
+        <v>0.2045</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>0.7796</v>
+        <v>0.2045</v>
       </c>
       <c r="N94" t="n">
-        <v>100000</v>
+        <v>101144.72</v>
       </c>
       <c r="O94" t="n">
-        <v>100779.59</v>
+        <v>101351.61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7688,25 +7688,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>97.714</v>
+        <v>0.8467</v>
       </c>
       <c r="H95" t="n">
-        <v>97.46899999999999</v>
+        <v>0.8436</v>
       </c>
       <c r="J95" t="n">
-        <v>97.875</v>
+        <v>0.8498</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7714,26 +7714,26 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.6571</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>0.6571</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>100779.59</v>
+        <v>101351.61</v>
       </c>
       <c r="O95" t="n">
-        <v>101441.86</v>
+        <v>102365.12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7742,25 +7742,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>99.376</v>
+        <v>116.5</v>
       </c>
       <c r="H96" t="n">
-        <v>99.571</v>
+        <v>116.79</v>
       </c>
       <c r="J96" t="n">
-        <v>99.014</v>
+        <v>116.15</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7768,26 +7768,26 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.8564</v>
+        <v>1.2069</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1.8564</v>
+        <v>1.2069</v>
       </c>
       <c r="N96" t="n">
-        <v>101441.86</v>
+        <v>100000</v>
       </c>
       <c r="O96" t="n">
-        <v>103325.03</v>
+        <v>101206.9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7796,25 +7796,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H97" t="n">
-        <v>99.46599999999999</v>
+        <v>118.16</v>
       </c>
       <c r="J97" t="n">
-        <v>99.218</v>
+        <v>117.9</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7822,26 +7822,26 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.7556</v>
+        <v>0.8571</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1.7556</v>
+        <v>0.8571</v>
       </c>
       <c r="N97" t="n">
-        <v>103325.03</v>
+        <v>101206.9</v>
       </c>
       <c r="O97" t="n">
-        <v>105138.96</v>
+        <v>102074.38</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -7850,25 +7850,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>99.246</v>
+        <v>118.08</v>
       </c>
       <c r="H98" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="J98" t="n">
-        <v>98.96899999999999</v>
+        <v>117.84</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7876,16 +7876,16 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.0863</v>
+        <v>3</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1.0863</v>
+        <v>3</v>
       </c>
       <c r="N98" t="n">
-        <v>105138.96</v>
+        <v>102074.38</v>
       </c>
       <c r="O98" t="n">
-        <v>106281.06</v>
+        <v>105136.62</v>
       </c>
     </row>
     <row r="99">
@@ -7895,34 +7895,34 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="J99" t="n">
-        <v>100.024</v>
+        <v>98.005</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7930,16 +7930,16 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.3111</v>
+        <v>0.7796</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>0.3111</v>
+        <v>0.7796</v>
       </c>
       <c r="N99" t="n">
-        <v>106281.06</v>
+        <v>100000</v>
       </c>
       <c r="O99" t="n">
-        <v>106611.71</v>
+        <v>100779.59</v>
       </c>
     </row>
     <row r="100">
@@ -7949,34 +7949,34 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H100" t="n">
-        <v>100.316</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>99.849</v>
+        <v>97.875</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7984,16 +7984,16 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.868</v>
+        <v>0.6571</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>0.868</v>
+        <v>0.6571</v>
       </c>
       <c r="N100" t="n">
-        <v>106611.71</v>
+        <v>100779.59</v>
       </c>
       <c r="O100" t="n">
-        <v>107537.1</v>
+        <v>101441.86</v>
       </c>
     </row>
     <row r="101">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -8012,25 +8012,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H101" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="J101" t="n">
-        <v>99.866</v>
+        <v>99.014</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -8038,16 +8038,16 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.678</v>
+        <v>1.8564</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0.678</v>
+        <v>1.8564</v>
       </c>
       <c r="N101" t="n">
-        <v>107537.1</v>
+        <v>101441.86</v>
       </c>
       <c r="O101" t="n">
-        <v>108266.17</v>
+        <v>103325.03</v>
       </c>
     </row>
     <row r="102">
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -8066,25 +8066,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>100.621</v>
+        <v>99.376</v>
       </c>
       <c r="H102" t="n">
-        <v>100.911</v>
+        <v>99.46599999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>100.618</v>
+        <v>99.218</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8092,16 +8092,16 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0.0103</v>
+        <v>1.7556</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>0.0103</v>
+        <v>1.7556</v>
       </c>
       <c r="N102" t="n">
-        <v>108266.17</v>
+        <v>103325.03</v>
       </c>
       <c r="O102" t="n">
-        <v>108277.37</v>
+        <v>105138.96</v>
       </c>
     </row>
     <row r="103">
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -8120,25 +8120,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>101.411</v>
+        <v>99.246</v>
       </c>
       <c r="H103" t="n">
-        <v>101.526</v>
+        <v>99.501</v>
       </c>
       <c r="J103" t="n">
-        <v>101.193</v>
+        <v>98.96899999999999</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8146,16 +8146,16 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8957</v>
+        <v>1.0863</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1.8957</v>
+        <v>1.0863</v>
       </c>
       <c r="N103" t="n">
-        <v>108277.37</v>
+        <v>105138.96</v>
       </c>
       <c r="O103" t="n">
-        <v>110329.93</v>
+        <v>106281.06</v>
       </c>
     </row>
     <row r="104">
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -8174,25 +8174,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H104" t="n">
-        <v>101.491</v>
+        <v>100.201</v>
       </c>
       <c r="J104" t="n">
-        <v>101.266</v>
+        <v>100.024</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8200,26 +8200,26 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.8125</v>
+        <v>0.3111</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1.8125</v>
+        <v>0.3111</v>
       </c>
       <c r="N104" t="n">
-        <v>110329.93</v>
+        <v>106281.06</v>
       </c>
       <c r="O104" t="n">
-        <v>112329.66</v>
+        <v>106611.71</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -8228,25 +8228,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H105" t="n">
-        <v>123.03</v>
+        <v>100.316</v>
       </c>
       <c r="J105" t="n">
-        <v>121.43</v>
+        <v>99.849</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8254,69 +8254,339 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0.2214</v>
+        <v>0.868</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>0.2214</v>
+        <v>0.868</v>
       </c>
       <c r="N105" t="n">
-        <v>100000</v>
+        <v>106611.71</v>
       </c>
       <c r="O105" t="n">
-        <v>100221.37</v>
+        <v>107537.1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>8</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>100.066</v>
+      </c>
+      <c r="H106" t="n">
+        <v>100.361</v>
+      </c>
+      <c r="J106" t="n">
+        <v>99.866</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="N106" t="n">
+        <v>107537.1</v>
+      </c>
+      <c r="O106" t="n">
+        <v>108266.17</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>9</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H107" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="J107" t="n">
+        <v>100.618</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="N107" t="n">
+        <v>108266.17</v>
+      </c>
+      <c r="O107" t="n">
+        <v>108277.37</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>10</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H108" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J108" t="n">
+        <v>101.193</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1.8957</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>1.8957</v>
+      </c>
+      <c r="N108" t="n">
+        <v>108277.37</v>
+      </c>
+      <c r="O108" t="n">
+        <v>110329.93</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>11</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H109" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J109" t="n">
+        <v>101.266</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="N109" t="n">
+        <v>110329.93</v>
+      </c>
+      <c r="O109" t="n">
+        <v>112329.66</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H110" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J110" t="n">
+        <v>121.43</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="N110" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O110" t="n">
+        <v>100221.37</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
         <v>2</v>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
         <v>130.16</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H111" t="n">
         <v>130.94</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J111" t="n">
         <v>127.25</v>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>exit_close</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
         <v>3.7308</v>
       </c>
-      <c r="M106" s="2" t="n">
+      <c r="M111" s="2" t="n">
         <v>3.7308</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N111" t="n">
         <v>100221.37</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O111" t="n">
         <v>103960.4</v>
       </c>
     </row>

--- a/output/quickfixclose0_all_markets_daily.xlsx
+++ b/output/quickfixclose0_all_markets_daily.xlsx
@@ -549,11 +549,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -597,11 +597,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -645,11 +645,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
         <v>11</v>
@@ -693,11 +693,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -741,11 +741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -789,11 +789,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -826,28 +826,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -865,37 +865,37 @@
         <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.57</v>
+        <v>7.35</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106568.21</v>
+        <v>107352.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -913,37 +913,37 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.42</v>
+        <v>6.97</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106418.3</v>
+        <v>106967.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.14</v>
+        <v>6.42</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>105136.62</v>
+        <v>106418.3</v>
       </c>
     </row>
     <row r="11">
@@ -981,17 +981,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1009,37 +1009,37 @@
         <v>100</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>104999.08</v>
+        <v>105340.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1057,37 +1057,37 @@
         <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3.8</v>
+        <v>5.14</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>103796.61</v>
+        <v>105136.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1105,10 +1105,10 @@
         <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>103503.61</v>
+        <v>103796.61</v>
       </c>
     </row>
     <row r="14">
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -1173,11 +1173,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1221,11 +1221,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfixclose0 daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6055,11 +6055,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6068,25 +6068,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H65" t="n">
-        <v>3.354</v>
+        <v>6.7656</v>
       </c>
       <c r="J65" t="n">
-        <v>3.295</v>
+        <v>6.591</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6094,16 +6094,16 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.2041</v>
+        <v>3.7189</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.2041</v>
+        <v>3.7189</v>
       </c>
       <c r="N65" t="n">
-        <v>100000</v>
+        <v>103503.61</v>
       </c>
       <c r="O65" t="n">
-        <v>100204.08</v>
+        <v>107352.83</v>
       </c>
     </row>
     <row r="66">
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -6137,10 +6137,10 @@
         <v>3.305</v>
       </c>
       <c r="H66" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J66" t="n">
-        <v>3.212</v>
+        <v>3.295</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6148,16 +6148,16 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.8235</v>
+        <v>0.2041</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1.8235</v>
+        <v>0.2041</v>
       </c>
       <c r="N66" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O66" t="n">
         <v>100204.08</v>
-      </c>
-      <c r="O66" t="n">
-        <v>102031.33</v>
       </c>
     </row>
     <row r="67">
@@ -6167,34 +6167,34 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H67" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J67" t="n">
-        <v>2.722</v>
+        <v>3.212</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6202,26 +6202,26 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.28</v>
+        <v>1.8235</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.28</v>
+        <v>1.8235</v>
       </c>
       <c r="N67" t="n">
+        <v>100204.08</v>
+      </c>
+      <c r="O67" t="n">
         <v>102031.33</v>
-      </c>
-      <c r="O67" t="n">
-        <v>103337.33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6230,25 +6230,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H68" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J68" t="n">
-        <v>1385.9</v>
+        <v>2.722</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6256,16 +6256,16 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="N68" t="n">
-        <v>100000</v>
+        <v>102031.33</v>
       </c>
       <c r="O68" t="n">
-        <v>101500</v>
+        <v>103337.33</v>
       </c>
     </row>
     <row r="69">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6284,25 +6284,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H69" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J69" t="n">
-        <v>1193.2</v>
+        <v>1385.9</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6310,53 +6310,53 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.4474</v>
+        <v>1.5</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3.4474</v>
+        <v>1.5</v>
       </c>
       <c r="N69" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O69" t="n">
         <v>101500</v>
-      </c>
-      <c r="O69" t="n">
-        <v>104999.08</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H70" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J70" t="n">
-        <v>2062.3</v>
+        <v>1193.2</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6364,53 +6364,53 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.7663</v>
+        <v>3.4474</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.7663</v>
+        <v>3.4474</v>
       </c>
       <c r="N70" t="n">
-        <v>100000</v>
+        <v>101500</v>
       </c>
       <c r="O70" t="n">
-        <v>100766.32</v>
+        <v>104999.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H71" t="n">
-        <v>1621</v>
+        <v>1412.1</v>
       </c>
       <c r="J71" t="n">
-        <v>1662</v>
+        <v>1378.3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6418,16 +6418,16 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0.3255</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1</v>
+        <v>0.3255</v>
       </c>
       <c r="N71" t="n">
-        <v>100766.32</v>
+        <v>104999.08</v>
       </c>
       <c r="O71" t="n">
-        <v>101773.99</v>
+        <v>105340.84</v>
       </c>
     </row>
     <row r="72">
@@ -6437,34 +6437,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H72" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="J72" t="n">
-        <v>1603</v>
+        <v>2062.3</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6472,16 +6472,16 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.6342</v>
+        <v>0.7663</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.6342</v>
+        <v>0.7663</v>
       </c>
       <c r="N72" t="n">
-        <v>101773.99</v>
+        <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>102419.46</v>
+        <v>100766.32</v>
       </c>
     </row>
     <row r="73">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -6500,25 +6500,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>1559</v>
+        <v>1641.5</v>
       </c>
       <c r="H73" t="n">
-        <v>1539.5</v>
+        <v>1621</v>
       </c>
       <c r="J73" t="n">
-        <v>1599.9</v>
+        <v>1662</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6526,16 +6526,16 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.0974</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2.0974</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>102419.46</v>
+        <v>100766.32</v>
       </c>
       <c r="O73" t="n">
-        <v>104567.64</v>
+        <v>101773.99</v>
       </c>
     </row>
     <row r="74">
@@ -6545,34 +6545,34 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1769.6</v>
+        <v>1581.5</v>
       </c>
       <c r="H74" t="n">
-        <v>1798.4</v>
+        <v>1547.6</v>
       </c>
       <c r="J74" t="n">
-        <v>1746.9</v>
+        <v>1603</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.7882</v>
+        <v>0.6342</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.7882</v>
+        <v>0.6342</v>
       </c>
       <c r="N74" t="n">
-        <v>104567.64</v>
+        <v>101773.99</v>
       </c>
       <c r="O74" t="n">
-        <v>105391.83</v>
+        <v>102419.46</v>
       </c>
     </row>
     <row r="75">
@@ -6599,34 +6599,34 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1769.6</v>
+        <v>1559</v>
       </c>
       <c r="H75" t="n">
-        <v>1798</v>
+        <v>1539.5</v>
       </c>
       <c r="J75" t="n">
-        <v>1737.9</v>
+        <v>1599.9</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6634,26 +6634,26 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.1162</v>
+        <v>2.0974</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1.1162</v>
+        <v>2.0974</v>
       </c>
       <c r="N75" t="n">
-        <v>105391.83</v>
+        <v>102419.46</v>
       </c>
       <c r="O75" t="n">
-        <v>106568.21</v>
+        <v>104567.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6662,25 +6662,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>27907</v>
+        <v>1769.6</v>
       </c>
       <c r="H76" t="n">
-        <v>27965.76</v>
+        <v>1798.4</v>
       </c>
       <c r="J76" t="n">
-        <v>27776</v>
+        <v>1746.9</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6688,26 +6688,26 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.2294</v>
+        <v>0.7882</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.2294</v>
+        <v>0.7882</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>104567.64</v>
       </c>
       <c r="O76" t="n">
-        <v>102229.41</v>
+        <v>105391.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6716,25 +6716,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H77" t="n">
-        <v>30074.01</v>
+        <v>1798</v>
       </c>
       <c r="J77" t="n">
-        <v>29615</v>
+        <v>1737.9</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6742,26 +6742,26 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.533</v>
+        <v>1.1162</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1.533</v>
+        <v>1.1162</v>
       </c>
       <c r="N77" t="n">
-        <v>102229.41</v>
+        <v>105391.83</v>
       </c>
       <c r="O77" t="n">
-        <v>103796.61</v>
+        <v>106568.21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6770,25 +6770,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H78" t="n">
-        <v>7223.26</v>
+        <v>1796.3</v>
       </c>
       <c r="J78" t="n">
-        <v>7171</v>
+        <v>1759.6</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6796,26 +6796,26 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.1275</v>
+        <v>0.3745</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2.1275</v>
+        <v>0.3745</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>106568.21</v>
       </c>
       <c r="O78" t="n">
-        <v>102127.47</v>
+        <v>106967.35</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6824,25 +6824,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>7773</v>
+        <v>27907</v>
       </c>
       <c r="H79" t="n">
-        <v>7820.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J79" t="n">
-        <v>7749.5</v>
+        <v>27776</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6850,26 +6850,26 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.4972</v>
+        <v>2.2294</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0.4972</v>
+        <v>2.2294</v>
       </c>
       <c r="N79" t="n">
-        <v>102127.47</v>
+        <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>102635.3</v>
+        <v>102229.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6878,25 +6878,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>6957.43</v>
+        <v>29892.8</v>
       </c>
       <c r="H80" t="n">
-        <v>6965.7</v>
+        <v>30074.01</v>
       </c>
       <c r="J80" t="n">
-        <v>6920.93</v>
+        <v>29615</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6904,26 +6904,26 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.4135</v>
+        <v>1.533</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4.4135</v>
+        <v>1.533</v>
       </c>
       <c r="N80" t="n">
-        <v>100000</v>
+        <v>102229.41</v>
       </c>
       <c r="O80" t="n">
-        <v>104413.54</v>
+        <v>103796.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6932,25 +6932,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H81" t="n">
-        <v>6988.83</v>
+        <v>7223.26</v>
       </c>
       <c r="J81" t="n">
-        <v>6978.6</v>
+        <v>7171</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6958,26 +6958,26 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.591</v>
+        <v>2.1275</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>0.591</v>
+        <v>2.1275</v>
       </c>
       <c r="N81" t="n">
-        <v>104413.54</v>
+        <v>100000</v>
       </c>
       <c r="O81" t="n">
-        <v>105030.61</v>
+        <v>102127.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6986,25 +6986,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H82" t="n">
-        <v>6992.85</v>
+        <v>7820.26</v>
       </c>
       <c r="J82" t="n">
-        <v>6969.01</v>
+        <v>7749.5</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7012,16 +7012,16 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.2813</v>
+        <v>0.4972</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1.2813</v>
+        <v>0.4972</v>
       </c>
       <c r="N82" t="n">
-        <v>105030.61</v>
+        <v>102127.47</v>
       </c>
       <c r="O82" t="n">
-        <v>106376.4</v>
+        <v>102635.3</v>
       </c>
     </row>
     <row r="83">
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -7040,25 +7040,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H83" t="n">
-        <v>6991.93</v>
+        <v>6965.7</v>
       </c>
       <c r="J83" t="n">
-        <v>6976.44</v>
+        <v>6920.93</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7066,16 +7066,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.6254</v>
+        <v>4.4135</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.6254</v>
+        <v>4.4135</v>
       </c>
       <c r="N83" t="n">
-        <v>106376.4</v>
+        <v>100000</v>
       </c>
       <c r="O83" t="n">
-        <v>107041.68</v>
+        <v>104413.54</v>
       </c>
     </row>
     <row r="84">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -7109,10 +7109,10 @@
         <v>6982.4</v>
       </c>
       <c r="H84" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="J84" t="n">
-        <v>6941.81</v>
+        <v>6978.6</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7120,16 +7120,16 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>9.1419</v>
+        <v>0.591</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>9.1419</v>
+        <v>0.591</v>
       </c>
       <c r="N84" t="n">
-        <v>107041.68</v>
+        <v>104413.54</v>
       </c>
       <c r="O84" t="n">
-        <v>116827.31</v>
+        <v>105030.61</v>
       </c>
     </row>
     <row r="85">
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7148,12 +7148,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -7163,10 +7163,10 @@
         <v>6982.4</v>
       </c>
       <c r="H85" t="n">
-        <v>6993.49</v>
+        <v>6992.85</v>
       </c>
       <c r="J85" t="n">
-        <v>6941.47</v>
+        <v>6969.01</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7174,16 +7174,16 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.6907</v>
+        <v>1.2813</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3.6907</v>
+        <v>1.2813</v>
       </c>
       <c r="N85" t="n">
-        <v>116827.31</v>
+        <v>105030.61</v>
       </c>
       <c r="O85" t="n">
-        <v>121139.07</v>
+        <v>106376.4</v>
       </c>
     </row>
     <row r="86">
@@ -7193,34 +7193,34 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H86" t="n">
-        <v>6770.77</v>
+        <v>6991.93</v>
       </c>
       <c r="J86" t="n">
-        <v>6830.71</v>
+        <v>6976.44</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7228,26 +7228,26 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.5366</v>
+        <v>0.6254</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1.5366</v>
+        <v>0.6254</v>
       </c>
       <c r="N86" t="n">
-        <v>121139.07</v>
+        <v>106376.4</v>
       </c>
       <c r="O86" t="n">
-        <v>123000.5</v>
+        <v>107041.68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7256,25 +7256,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H87" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="J87" t="n">
-        <v>85.59099999999999</v>
+        <v>6941.81</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7282,53 +7282,53 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.2552</v>
+        <v>9.1419</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>0.2552</v>
+        <v>9.1419</v>
       </c>
       <c r="N87" t="n">
-        <v>100000</v>
+        <v>107041.68</v>
       </c>
       <c r="O87" t="n">
-        <v>100255.21</v>
+        <v>116827.31</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H88" t="n">
-        <v>71.999</v>
+        <v>6993.49</v>
       </c>
       <c r="J88" t="n">
-        <v>75.91200000000001</v>
+        <v>6941.47</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7336,53 +7336,53 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.1209</v>
+        <v>3.6907</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1.1209</v>
+        <v>3.6907</v>
       </c>
       <c r="N88" t="n">
-        <v>100255.21</v>
+        <v>116827.31</v>
       </c>
       <c r="O88" t="n">
-        <v>101378.94</v>
+        <v>121139.07</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>15</v>
+        <v>6794.4</v>
       </c>
       <c r="H89" t="n">
-        <v>15.26</v>
+        <v>6770.77</v>
       </c>
       <c r="J89" t="n">
-        <v>14.99</v>
+        <v>6830.71</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7390,26 +7390,26 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.0385</v>
+        <v>1.5366</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>0.0385</v>
+        <v>1.5366</v>
       </c>
       <c r="N89" t="n">
-        <v>100000</v>
+        <v>121139.07</v>
       </c>
       <c r="O89" t="n">
-        <v>100038.46</v>
+        <v>123000.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7418,25 +7418,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H90" t="n">
-        <v>15.18</v>
+        <v>88.001</v>
       </c>
       <c r="J90" t="n">
-        <v>14.85</v>
+        <v>85.59099999999999</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7444,53 +7444,53 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.8333</v>
+        <v>0.2552</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.2552</v>
       </c>
       <c r="N90" t="n">
-        <v>100038.46</v>
+        <v>100000</v>
       </c>
       <c r="O90" t="n">
-        <v>100872.12</v>
+        <v>100255.21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="J91" t="n">
-        <v>20.88</v>
+        <v>75.91200000000001</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7498,22 +7498,22 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.0556</v>
+        <v>1.1209</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0.0556</v>
+        <v>1.1209</v>
       </c>
       <c r="N91" t="n">
-        <v>100000</v>
+        <v>100255.21</v>
       </c>
       <c r="O91" t="n">
-        <v>100055.56</v>
+        <v>101378.94</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -7526,25 +7526,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H92" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8589</v>
+        <v>14.99</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7552,22 +7552,22 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.087</v>
+        <v>0.0385</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1.087</v>
+        <v>0.0385</v>
       </c>
       <c r="N92" t="n">
         <v>100000</v>
       </c>
       <c r="O92" t="n">
-        <v>101086.96</v>
+        <v>100038.46</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -7580,25 +7580,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H93" t="n">
-        <v>0.8649</v>
+        <v>15.18</v>
       </c>
       <c r="J93" t="n">
-        <v>0.8612</v>
+        <v>14.85</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7606,26 +7606,26 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.0571</v>
+        <v>0.8333</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>0.0571</v>
+        <v>0.8333</v>
       </c>
       <c r="N93" t="n">
-        <v>101086.96</v>
+        <v>100038.46</v>
       </c>
       <c r="O93" t="n">
-        <v>101144.72</v>
+        <v>100872.12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7634,25 +7634,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="J94" t="n">
-        <v>0.8605</v>
+        <v>20.88</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7660,16 +7660,16 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.2045</v>
+        <v>0.0556</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>0.2045</v>
+        <v>0.0556</v>
       </c>
       <c r="N94" t="n">
-        <v>101144.72</v>
+        <v>100000</v>
       </c>
       <c r="O94" t="n">
-        <v>101351.61</v>
+        <v>100055.56</v>
       </c>
     </row>
     <row r="95">
@@ -7679,34 +7679,34 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="J95" t="n">
-        <v>0.8498</v>
+        <v>0.8589</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7714,26 +7714,26 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>1.087</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1</v>
+        <v>1.087</v>
       </c>
       <c r="N95" t="n">
-        <v>101351.61</v>
+        <v>100000</v>
       </c>
       <c r="O95" t="n">
-        <v>102365.12</v>
+        <v>101086.96</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7742,25 +7742,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>116.79</v>
+        <v>0.8649</v>
       </c>
       <c r="J96" t="n">
-        <v>116.15</v>
+        <v>0.8612</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7768,26 +7768,26 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.2069</v>
+        <v>0.0571</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1.2069</v>
+        <v>0.0571</v>
       </c>
       <c r="N96" t="n">
-        <v>100000</v>
+        <v>101086.96</v>
       </c>
       <c r="O96" t="n">
-        <v>101206.9</v>
+        <v>101144.72</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7796,25 +7796,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>118.16</v>
+        <v>0.8658</v>
       </c>
       <c r="J97" t="n">
-        <v>117.9</v>
+        <v>0.8605</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7822,53 +7822,53 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.8571</v>
+        <v>0.2045</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>0.8571</v>
+        <v>0.2045</v>
       </c>
       <c r="N97" t="n">
-        <v>101206.9</v>
+        <v>101144.72</v>
       </c>
       <c r="O97" t="n">
-        <v>102074.38</v>
+        <v>101351.61</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>118.08</v>
+        <v>0.8467</v>
       </c>
       <c r="H98" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="J98" t="n">
-        <v>117.84</v>
+        <v>0.8498</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7876,22 +7876,22 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>102074.38</v>
+        <v>101351.61</v>
       </c>
       <c r="O98" t="n">
-        <v>105136.62</v>
+        <v>102365.12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -7899,30 +7899,30 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H99" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="J99" t="n">
-        <v>98.005</v>
+        <v>116.15</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7930,22 +7930,22 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.7796</v>
+        <v>1.2069</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>0.7796</v>
+        <v>1.2069</v>
       </c>
       <c r="N99" t="n">
         <v>100000</v>
       </c>
       <c r="O99" t="n">
-        <v>100779.59</v>
+        <v>101206.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -7953,30 +7953,30 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>97.714</v>
+        <v>118.02</v>
       </c>
       <c r="H100" t="n">
-        <v>97.46899999999999</v>
+        <v>118.16</v>
       </c>
       <c r="J100" t="n">
-        <v>97.875</v>
+        <v>117.9</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7984,22 +7984,22 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.6571</v>
+        <v>0.8571</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>0.6571</v>
+        <v>0.8571</v>
       </c>
       <c r="N100" t="n">
-        <v>100779.59</v>
+        <v>101206.9</v>
       </c>
       <c r="O100" t="n">
-        <v>101441.86</v>
+        <v>102074.38</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -8012,25 +8012,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>99.376</v>
+        <v>118.08</v>
       </c>
       <c r="H101" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="J101" t="n">
-        <v>99.014</v>
+        <v>117.84</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -8038,16 +8038,16 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.8564</v>
+        <v>3</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1.8564</v>
+        <v>3</v>
       </c>
       <c r="N101" t="n">
-        <v>101441.86</v>
+        <v>102074.38</v>
       </c>
       <c r="O101" t="n">
-        <v>103325.03</v>
+        <v>105136.62</v>
       </c>
     </row>
     <row r="102">
@@ -8057,34 +8057,34 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>99.376</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>99.46599999999999</v>
+        <v>97.569</v>
       </c>
       <c r="J102" t="n">
-        <v>99.218</v>
+        <v>98.005</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8092,16 +8092,16 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.7556</v>
+        <v>0.7796</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1.7556</v>
+        <v>0.7796</v>
       </c>
       <c r="N102" t="n">
-        <v>103325.03</v>
+        <v>100000</v>
       </c>
       <c r="O102" t="n">
-        <v>105138.96</v>
+        <v>100779.59</v>
       </c>
     </row>
     <row r="103">
@@ -8111,34 +8111,34 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>99.246</v>
+        <v>97.714</v>
       </c>
       <c r="H103" t="n">
-        <v>99.501</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>98.96899999999999</v>
+        <v>97.875</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8146,16 +8146,16 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.0863</v>
+        <v>0.6571</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1.0863</v>
+        <v>0.6571</v>
       </c>
       <c r="N103" t="n">
-        <v>105138.96</v>
+        <v>100779.59</v>
       </c>
       <c r="O103" t="n">
-        <v>106281.06</v>
+        <v>101441.86</v>
       </c>
     </row>
     <row r="104">
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -8174,25 +8174,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H104" t="n">
-        <v>100.201</v>
+        <v>99.571</v>
       </c>
       <c r="J104" t="n">
-        <v>100.024</v>
+        <v>99.014</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8200,16 +8200,16 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.3111</v>
+        <v>1.8564</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>0.3111</v>
+        <v>1.8564</v>
       </c>
       <c r="N104" t="n">
-        <v>106281.06</v>
+        <v>101441.86</v>
       </c>
       <c r="O104" t="n">
-        <v>106611.71</v>
+        <v>103325.03</v>
       </c>
     </row>
     <row r="105">
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -8228,25 +8228,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H105" t="n">
-        <v>100.316</v>
+        <v>99.46599999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>99.849</v>
+        <v>99.218</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8254,16 +8254,16 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0.868</v>
+        <v>1.7556</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>0.868</v>
+        <v>1.7556</v>
       </c>
       <c r="N105" t="n">
-        <v>106611.71</v>
+        <v>103325.03</v>
       </c>
       <c r="O105" t="n">
-        <v>107537.1</v>
+        <v>105138.96</v>
       </c>
     </row>
     <row r="106">
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -8282,25 +8282,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H106" t="n">
-        <v>100.361</v>
+        <v>99.501</v>
       </c>
       <c r="J106" t="n">
-        <v>99.866</v>
+        <v>98.96899999999999</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8308,16 +8308,16 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.678</v>
+        <v>1.0863</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>0.678</v>
+        <v>1.0863</v>
       </c>
       <c r="N106" t="n">
-        <v>107537.1</v>
+        <v>105138.96</v>
       </c>
       <c r="O106" t="n">
-        <v>108266.17</v>
+        <v>106281.06</v>
       </c>
     </row>
     <row r="107">
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -8336,25 +8336,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H107" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="J107" t="n">
-        <v>100.618</v>
+        <v>100.024</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8362,16 +8362,16 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.0103</v>
+        <v>0.3111</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.3111</v>
       </c>
       <c r="N107" t="n">
-        <v>108266.17</v>
+        <v>106281.06</v>
       </c>
       <c r="O107" t="n">
-        <v>108277.37</v>
+        <v>106611.71</v>
       </c>
     </row>
     <row r="108">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -8390,25 +8390,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H108" t="n">
-        <v>101.526</v>
+        <v>100.316</v>
       </c>
       <c r="J108" t="n">
-        <v>101.193</v>
+        <v>99.849</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8416,16 +8416,16 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.8957</v>
+        <v>0.868</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1.8957</v>
+        <v>0.868</v>
       </c>
       <c r="N108" t="n">
-        <v>108277.37</v>
+        <v>106611.71</v>
       </c>
       <c r="O108" t="n">
-        <v>110329.93</v>
+        <v>107537.1</v>
       </c>
     </row>
     <row r="109">
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -8444,25 +8444,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H109" t="n">
-        <v>101.491</v>
+        <v>100.361</v>
       </c>
       <c r="J109" t="n">
-        <v>101.266</v>
+        <v>99.866</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8470,26 +8470,26 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.8125</v>
+        <v>0.678</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1.8125</v>
+        <v>0.678</v>
       </c>
       <c r="N109" t="n">
-        <v>110329.93</v>
+        <v>107537.1</v>
       </c>
       <c r="O109" t="n">
-        <v>112329.66</v>
+        <v>108266.17</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -8498,25 +8498,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>121.72</v>
+        <v>100.621</v>
       </c>
       <c r="H110" t="n">
-        <v>123.03</v>
+        <v>100.911</v>
       </c>
       <c r="J110" t="n">
-        <v>121.43</v>
+        <v>100.618</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8524,69 +8524,231 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.2214</v>
+        <v>0.0103</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>0.2214</v>
+        <v>0.0103</v>
       </c>
       <c r="N110" t="n">
-        <v>100000</v>
+        <v>108266.17</v>
       </c>
       <c r="O110" t="n">
-        <v>100221.37</v>
+        <v>108277.37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H111" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J111" t="n">
+        <v>101.193</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1.8957</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1.8957</v>
+      </c>
+      <c r="N111" t="n">
+        <v>108277.37</v>
+      </c>
+      <c r="O111" t="n">
+        <v>110329.93</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H112" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J112" t="n">
+        <v>101.266</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="N112" t="n">
+        <v>110329.93</v>
+      </c>
+      <c r="O112" t="n">
+        <v>112329.66</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H113" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J113" t="n">
+        <v>121.43</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="N113" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O113" t="n">
+        <v>100221.37</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
         <v>2</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
         <v>130.16</v>
       </c>
-      <c r="H111" t="n">
+      <c r="H114" t="n">
         <v>130.94</v>
       </c>
-      <c r="J111" t="n">
+      <c r="J114" t="n">
         <v>127.25</v>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>exit_close</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
         <v>3.7308</v>
       </c>
-      <c r="M111" s="2" t="n">
+      <c r="M114" s="2" t="n">
         <v>3.7308</v>
       </c>
-      <c r="N111" t="n">
+      <c r="N114" t="n">
         <v>100221.37</v>
       </c>
-      <c r="O111" t="n">
+      <c r="O114" t="n">
         <v>103960.4</v>
       </c>
     </row>
